--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121174622</v>
+        <v>121159308</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,30 +710,30 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Hyttsjön, Vstm</t>
+          <t>Söder om Hyttjärn #1, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546891</v>
+        <v>546748</v>
       </c>
       <c r="R2" t="n">
-        <v>6664341</v>
+        <v>6664293</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +803,7 @@
         <v>121160161</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159308</v>
+        <v>121174622</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,30 +960,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Hyttjärn #1, Vstm</t>
+          <t>Söder om Hyttsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546748</v>
+        <v>546891</v>
       </c>
       <c r="R4" t="n">
-        <v>6664293</v>
+        <v>6664341</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121187430</v>
+        <v>121187449</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,27 +1085,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
+          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546789</v>
+        <v>546748</v>
       </c>
       <c r="R5" t="n">
-        <v>6664279</v>
+        <v>6664294</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>U-Nor-0319</t>
+          <t>U-Nor-0320</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1174,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121187449</v>
+        <v>121187430</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,31 +1213,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
+          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546748</v>
+        <v>546789</v>
       </c>
       <c r="R6" t="n">
-        <v>6664294</v>
+        <v>6664279</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Nor-0320</t>
+          <t>U-Nor-0319</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121159308</v>
+        <v>121160161</v>
       </c>
       <c r="B2" t="n">
         <v>98081</v>
@@ -710,27 +710,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Hyttjärn #1, Vstm</t>
+          <t>Söder om Hyttsjön, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546748</v>
+        <v>546788</v>
       </c>
       <c r="R2" t="n">
-        <v>6664293</v>
+        <v>6664279</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121160161</v>
+        <v>121159308</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -835,27 +835,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Hyttsjön, Vstm</t>
+          <t>Söder om Hyttjärn #1, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546788</v>
+        <v>546748</v>
       </c>
       <c r="R3" t="n">
-        <v>6664279</v>
+        <v>6664293</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121187449</v>
+        <v>121187430</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1085,31 +1085,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
+          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546748</v>
+        <v>546789</v>
       </c>
       <c r="R5" t="n">
-        <v>6664294</v>
+        <v>6664279</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1136,7 +1132,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>U-Nor-0320</t>
+          <t>U-Nor-0319</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1178,7 +1174,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121187430</v>
+        <v>121187449</v>
       </c>
       <c r="B6" t="n">
         <v>98081</v>
@@ -1213,27 +1209,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
+          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546789</v>
+        <v>546748</v>
       </c>
       <c r="R6" t="n">
-        <v>6664279</v>
+        <v>6664294</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Nor-0319</t>
+          <t>U-Nor-0320</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121160161</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121159308</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>121174622</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121187430</v>
+        <v>121187449</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,27 +1085,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
+          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546789</v>
+        <v>546748</v>
       </c>
       <c r="R5" t="n">
-        <v>6664279</v>
+        <v>6664294</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>U-Nor-0319</t>
+          <t>U-Nor-0320</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1174,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121187449</v>
+        <v>121187430</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,31 +1213,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
+          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546748</v>
+        <v>546789</v>
       </c>
       <c r="R6" t="n">
-        <v>6664294</v>
+        <v>6664279</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Nor-0320</t>
+          <t>U-Nor-0319</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121160161</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>121159308</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>121174622</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121187449</v>
+        <v>121187430</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,31 +1085,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
+          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546748</v>
+        <v>546789</v>
       </c>
       <c r="R5" t="n">
-        <v>6664294</v>
+        <v>6664279</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1136,7 +1132,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>U-Nor-0320</t>
+          <t>U-Nor-0319</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1178,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121187430</v>
+        <v>121187449</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,27 +1209,31 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
+          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546789</v>
+        <v>546748</v>
       </c>
       <c r="R6" t="n">
-        <v>6664279</v>
+        <v>6664294</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Nor-0319</t>
+          <t>U-Nor-0320</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121160161</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121159308</v>
+        <v>121174622</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,30 +835,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder om Hyttjärn #1, Vstm</t>
+          <t>Söder om Hyttsjön, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546748</v>
+        <v>546891</v>
       </c>
       <c r="R3" t="n">
-        <v>6664293</v>
+        <v>6664341</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121174622</v>
+        <v>121159308</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,30 +960,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Hyttsjön, Vstm</t>
+          <t>Söder om Hyttjärn #1, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546891</v>
+        <v>546748</v>
       </c>
       <c r="R4" t="n">
-        <v>6664341</v>
+        <v>6664293</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
         <v>121187430</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>121187449</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121187430</v>
+        <v>121187449</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1085,27 +1085,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
+          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546789</v>
+        <v>546748</v>
       </c>
       <c r="R5" t="n">
-        <v>6664279</v>
+        <v>6664294</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>U-Nor-0319</t>
+          <t>U-Nor-0320</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1174,7 +1178,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121187449</v>
+        <v>121187430</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1209,31 +1213,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hyttsjön, S om 3 (knärot), Vstm</t>
+          <t>Hyttsjön, SO om 2 (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546748</v>
+        <v>546789</v>
       </c>
       <c r="R6" t="n">
-        <v>6664294</v>
+        <v>6664279</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>U-Nor-0320</t>
+          <t>U-Nor-0319</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">

--- a/artfynd/A 41468-2024 artfynd.xlsx
+++ b/artfynd/A 41468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121160161</v>
+        <v>121159308</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,27 +710,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder om Hyttsjön, Vstm</t>
+          <t>Söder om Hyttjärn #1, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546788</v>
+        <v>546748</v>
       </c>
       <c r="R2" t="n">
-        <v>6664279</v>
+        <v>6664293</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121174622</v>
+        <v>121160161</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546891</v>
+        <v>546788</v>
       </c>
       <c r="R3" t="n">
-        <v>6664341</v>
+        <v>6664279</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159308</v>
+        <v>121174622</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,30 +960,30 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Hyttjärn #1, Vstm</t>
+          <t>Söder om Hyttsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546748</v>
+        <v>546891</v>
       </c>
       <c r="R4" t="n">
-        <v>6664293</v>
+        <v>6664341</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
         <v>121187449</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>121187430</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
